--- a/sharing_consent_forms/003_educational_material_translation_consent_form--sharing_consent_forms.xlsx
+++ b/sharing_consent_forms/003_educational_material_translation_consent_form--sharing_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'portuguese'}</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Portuguese'}</t>
+          <t>Portuguese</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'arabic'}</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Arabic'}</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'russian'}</t>
+          <t>russian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Russian'}</t>
+          <t>Russian</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'german'}</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'German'}</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'korean'}</t>
+          <t>korean</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Korean'}</t>
+          <t>Korean</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'japanese'}</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Japanese'}</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'italian'}</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Italian'}</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'machine_translation'}</t>
+          <t>machine_translation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Machine Translation'}</t>
+          <t>Machine Translation</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'human_translation'}</t>
+          <t>human_translation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Human Translation'}</t>
+          <t>Human Translation</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
